--- a/data/trans_orig/P15B_3_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P15B_3_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2007</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2007 (tasa de respuesta: 51,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12630</t>
+          <t>12614</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17549</t>
+          <t>18053</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12544</t>
+          <t>12560</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21985</t>
+          <t>21876</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37987</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44604</t>
+          <t>44579</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53153</t>
+          <t>52649</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65412</t>
+          <t>65341</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20446</t>
+          <t>21592</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38058</t>
+          <t>38098</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24852</t>
+          <t>25808</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44214</t>
+          <t>44713</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40445</t>
+          <t>40405</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58057</t>
+          <t>56911</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24806</t>
+          <t>24838</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33141</t>
+          <t>33203</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69332</t>
+          <t>68833</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>88694</t>
+          <t>87738</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11135</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>11025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21501</t>
+          <t>21822</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32636</t>
+          <t>31647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29670</t>
+          <t>30208</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51103</t>
+          <t>50354</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17783</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37066</t>
+          <t>36767</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63918</t>
+          <t>62093</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71974</t>
+          <t>72723</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93407</t>
+          <t>92869</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76023</t>
+          <t>76731</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88843</t>
+          <t>89103</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152965</t>
+          <t>154790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>179817</t>
+          <t>180116</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2012</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2012 (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11600</t>
+          <t>11228</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26374</t>
+          <t>26242</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29673</t>
+          <t>31226</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50366</t>
+          <t>50498</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65140</t>
+          <t>65512</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105410</t>
+          <t>105837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160004</t>
+          <t>158451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177223</t>
+          <t>177281</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29280</t>
+          <t>28225</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51878</t>
+          <t>49994</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14071</t>
+          <t>14135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35653</t>
+          <t>35265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61212</t>
+          <t>59696</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>131406</t>
+          <t>133290</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154004</t>
+          <t>155059</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99622</t>
+          <t>99558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110624</t>
+          <t>110472</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>235765</t>
+          <t>237281</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>261324</t>
+          <t>261712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,13%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16442</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>16285</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24189</t>
+          <t>24207</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>18655</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38387</t>
+          <t>38046</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50693</t>
+          <t>50792</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48994</t>
+          <t>48256</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78043</t>
+          <t>76938</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23649</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60870</t>
+          <t>60488</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94229</t>
+          <t>92858</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>208035</t>
+          <t>209140</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237084</t>
+          <t>237822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231756</t>
+          <t>232272</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>248464</t>
+          <t>248844</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>447253</t>
+          <t>448624</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>480612</t>
+          <t>480994</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2016</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2016 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13676</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34463</t>
+          <t>35115</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43003</t>
+          <t>42972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67257</t>
+          <t>67356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105822</t>
+          <t>106593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116469</t>
+          <t>116535</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13875</t>
+          <t>14440</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31699</t>
+          <t>31937</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14491</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>19915</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39395</t>
+          <t>39941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88423</t>
+          <t>88185</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>106247</t>
+          <t>105682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71354</t>
+          <t>71569</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82010</t>
+          <t>81958</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>166571</t>
+          <t>166025</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>187217</t>
+          <t>186051</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,33%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>8637</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13630</t>
+          <t>13744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>21784</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22228</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29971</t>
+          <t>29961</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48173</t>
+          <t>48059</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59235</t>
+          <t>58989</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19756</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39229</t>
+          <t>38531</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22882</t>
+          <t>21957</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31303</t>
+          <t>31227</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54913</t>
+          <t>56922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156586</t>
+          <t>157284</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176059</t>
+          <t>176246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168571</t>
+          <t>169496</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>183307</t>
+          <t>183533</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>332355</t>
+          <t>330346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>355965</t>
+          <t>356041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2023</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>5747</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>13366</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25550</t>
+          <t>25548</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33777</t>
+          <t>33690</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73788</t>
+          <t>73807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78538</t>
+          <t>78530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100885</t>
+          <t>101794</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111140</t>
+          <t>111473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24837</t>
+          <t>26676</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50140</t>
+          <t>50239</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6575</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20585</t>
+          <t>18949</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37001</t>
+          <t>35248</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66486</t>
+          <t>63724</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>27,58%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78973</t>
+          <t>78874</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104276</t>
+          <t>102437</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81372</t>
+          <t>83008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95271</t>
+          <t>95382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164584</t>
+          <t>167346</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194069</t>
+          <t>195822</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>769</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>10840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24086</t>
+          <t>24163</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26348</t>
+          <t>26350</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54223</t>
+          <t>53252</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62810</t>
+          <t>63323</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33865</t>
+          <t>33153</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61119</t>
+          <t>59617</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>24550</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47897</t>
+          <t>46430</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78398</t>
+          <t>78266</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136826</t>
+          <t>138328</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164080</t>
+          <t>164792</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>188525</t>
+          <t>187827</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202280</t>
+          <t>201839</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>331925</t>
+          <t>332057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>362426</t>
+          <t>363893</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15B_3_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P15B_3_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12614</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7588</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18053</t>
+          <t>17292</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12560</t>
+          <t>12179</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21876</t>
+          <t>21990</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37819</t>
+          <t>37940</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44579</t>
+          <t>44571</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52649</t>
+          <t>53410</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65341</t>
+          <t>65562</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21592</t>
+          <t>21520</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38098</t>
+          <t>38731</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25808</t>
+          <t>25667</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44713</t>
+          <t>44865</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40405</t>
+          <t>39772</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56911</t>
+          <t>56983</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>25038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33203</t>
+          <t>33170</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68833</t>
+          <t>68681</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87738</t>
+          <t>87879</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,4%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,44 +1439,44 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>45,75%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1522</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5713</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>43,17%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1522</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6926</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>52,33%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11025</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,49 +1547,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>54,25%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>11714</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7523</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>13236</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>88,5%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>56,83%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>11714</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>6310</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>13236</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,5%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>47,67%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>26</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>21637</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31647</t>
+          <t>31636</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30208</t>
+          <t>29880</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50354</t>
+          <t>51811</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36767</t>
+          <t>37616</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62093</t>
+          <t>62717</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72723</t>
+          <t>71266</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92869</t>
+          <t>93197</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76731</t>
+          <t>76808</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89103</t>
+          <t>89342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154790</t>
+          <t>154166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>180116</t>
+          <t>179267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,66%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>11707</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26242</t>
+          <t>28309</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12396</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31226</t>
+          <t>31088</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50498</t>
+          <t>48431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65512</t>
+          <t>65033</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105837</t>
+          <t>105579</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158451</t>
+          <t>158589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177281</t>
+          <t>177204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28225</t>
+          <t>28302</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49994</t>
+          <t>50611</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14135</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35265</t>
+          <t>34501</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59696</t>
+          <t>60344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133290</t>
+          <t>132673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155059</t>
+          <t>154982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99558</t>
+          <t>98362</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110472</t>
+          <t>110426</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>236633</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>261712</t>
+          <t>262476</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,38%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16783</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>16070</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24207</t>
+          <t>24200</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18655</t>
+          <t>18523</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38046</t>
+          <t>38308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50792</t>
+          <t>50935</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48256</t>
+          <t>48533</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76938</t>
+          <t>75625</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>23025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60488</t>
+          <t>61040</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92858</t>
+          <t>93855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>209140</t>
+          <t>210453</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237822</t>
+          <t>237545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>232272</t>
+          <t>232380</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>248844</t>
+          <t>248400</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>448624</t>
+          <t>447627</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>480994</t>
+          <t>480442</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,73%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9782</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12905</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35115</t>
+          <t>35025</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42972</t>
+          <t>43005</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67356</t>
+          <t>66789</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106593</t>
+          <t>106495</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116535</t>
+          <t>116720</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14440</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31937</t>
+          <t>31507</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14276</t>
+          <t>14608</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39941</t>
+          <t>41416</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88185</t>
+          <t>88615</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105682</t>
+          <t>106013</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71569</t>
+          <t>71237</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81958</t>
+          <t>81997</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>166025</t>
+          <t>164550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>186051</t>
+          <t>185840</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,23%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>8611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>983</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13744</t>
+          <t>12585</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>22185</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22370</t>
+          <t>21964</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29961</t>
+          <t>30024</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48059</t>
+          <t>49218</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58989</t>
+          <t>59163</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>19983</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38531</t>
+          <t>40105</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21957</t>
+          <t>22800</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31227</t>
+          <t>31693</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56922</t>
+          <t>57503</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157284</t>
+          <t>155710</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176246</t>
+          <t>175832</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>169496</t>
+          <t>168653</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>183533</t>
+          <t>183351</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>330346</t>
+          <t>329765</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>356041</t>
+          <t>355575</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>15171</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30597</t>
+          <t>32769</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25548</t>
+          <t>27135</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33690</t>
+          <t>36014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>76872</t>
+          <t>81792</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73807</t>
+          <t>78089</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78530</t>
+          <t>83531</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>107469</t>
+          <t>114561</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101794</t>
+          <t>107193</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111473</t>
+          <t>118225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35606</t>
+          <t>37843</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35606</t>
+          <t>37843</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35606</t>
+          <t>37843</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79554</t>
+          <t>84521</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79554</t>
+          <t>84521</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79554</t>
+          <t>84521</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>115160</t>
+          <t>122364</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115160</t>
+          <t>122364</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115160</t>
+          <t>122364</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37466</t>
+          <t>40162</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26676</t>
+          <t>28531</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50239</t>
+          <t>53262</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11766</t>
+          <t>12415</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>19991</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>49232</t>
+          <t>52577</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35248</t>
+          <t>39521</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63724</t>
+          <t>68675</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>91647</t>
+          <t>98944</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78874</t>
+          <t>85844</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102437</t>
+          <t>110575</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>90191</t>
+          <t>98612</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83008</t>
+          <t>91036</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95382</t>
+          <t>103818</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>181838</t>
+          <t>197557</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>167346</t>
+          <t>181459</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>195822</t>
+          <t>210613</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,2%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>129113</t>
+          <t>139106</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>129113</t>
+          <t>139106</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>129113</t>
+          <t>139106</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>101957</t>
+          <t>111027</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>101957</t>
+          <t>111027</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>101957</t>
+          <t>111027</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>231070</t>
+          <t>250134</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>231070</t>
+          <t>250134</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>231070</t>
+          <t>250134</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>11426</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -6336,27 +6336,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24163</t>
+          <t>31885</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6371,27 +6371,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29543</t>
+          <t>33813</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26350</t>
+          <t>30325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>59941</t>
+          <t>72505</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53252</t>
+          <t>65482</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63323</t>
+          <t>75697</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>64092</t>
+          <t>76908</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64092</t>
+          <t>76908</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>64092</t>
+          <t>76908</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45303</t>
+          <t>48213</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>34524</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59617</t>
+          <t>64476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24550</t>
+          <t>25125</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>61075</t>
+          <t>64782</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46430</t>
+          <t>49891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78266</t>
+          <t>82087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>152642</t>
+          <t>170404</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>138328</t>
+          <t>154141</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164792</t>
+          <t>184093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>196605</t>
+          <t>214218</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>187827</t>
+          <t>205663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201839</t>
+          <t>220792</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>349248</t>
+          <t>384623</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>332057</t>
+          <t>367318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>363893</t>
+          <t>399514</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,9%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>197945</t>
+          <t>218617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>197945</t>
+          <t>218617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>197945</t>
+          <t>218617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212377</t>
+          <t>230788</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212377</t>
+          <t>230788</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212377</t>
+          <t>230788</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>410323</t>
+          <t>449405</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>410323</t>
+          <t>449405</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>410323</t>
+          <t>449405</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
